--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,27 +541,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-474</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-511</t>
+          <t>Nile Air NP-330</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1535</v>
+        <v>1174</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-517</v>
+        <v>-898</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,27 +586,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-474</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-5111</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1535</v>
+        <v>1333</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-517</v>
+        <v>-739</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-474</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-179</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1845</v>
+        <v>1529</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-207</v>
+        <v>-543</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,27 +676,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-474</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1849</v>
+        <v>1535</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-203</v>
+        <v>-537</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,27 +721,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-474</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-975</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-203</v>
+        <v>-227</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-763</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>889</v>
+        <v>939</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1163</v>
+        <v>-1133</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>Nile Air NP-428</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>969</v>
+        <v>1174</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1083</v>
+        <v>-898</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>Nile Air NP-528</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>969</v>
+        <v>1333</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1083</v>
+        <v>-739</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-565</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>989</v>
+        <v>1333</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1063</v>
+        <v>-739</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-583</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>989</v>
+        <v>1333</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1063</v>
+        <v>-739</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>989</v>
+        <v>1349</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1063</v>
+        <v>-723</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>989</v>
+        <v>1349</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1063</v>
+        <v>-723</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-589</t>
+          <t>flyadeal F3-763</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>989</v>
+        <v>1349</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1063</v>
+        <v>-723</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-577</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>989</v>
+        <v>1535</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1063</v>
+        <v>-537</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>989</v>
+        <v>1535</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1063</v>
+        <v>-537</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-761</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1059</v>
+        <v>1535</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-993</v>
+        <v>-537</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,26 +1275,26 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1175</v>
+        <v>1539</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-877</v>
+        <v>-533</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,26 +1320,26 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1298</v>
+        <v>1820</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-754</v>
+        <v>-252</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-179</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1333</v>
+        <v>1845</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2052</v>
+        <v>2072</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-719</v>
+        <v>-227</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,33 +1406,8358 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-1029</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-959</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-907</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-907</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-364</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-898</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-817</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-727</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Nesma Airlines NE-171</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D28" s="2" t="n">
         <v>1535</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2052</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-517</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
+      <c r="E28" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-537</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-513</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-303</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1867</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-205</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-322</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1867</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-205</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1907</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1907</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-324</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-717</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-657</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-619</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-571</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-544</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-471</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-461</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-461</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-316</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-316</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-303</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-316</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-307</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-307</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-304</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1329</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-77</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>20-APR-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>476</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>03-MAY-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>16-MAY-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>1244</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-435</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>1244</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-435</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-646</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-660</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-430</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>582</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-410</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-205</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-646</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-660</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-973</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-973</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-903</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-903</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-903</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-893</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-893</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-893</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-893</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-793</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-793</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-793</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-772</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-772</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-772</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-772</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-707</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>951</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-641</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>952</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-640</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-557</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-557</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1058</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-534</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-303</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1222</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-370</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>1055</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-537</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-533</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>30-MAY-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1055</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>-759</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>-665</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-369</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-322</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-369</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>01-JUN-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>-443</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>-703</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1292</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>-533</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>-503</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>681</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>-911</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>-896</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>969</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>-623</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>681</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>896</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>-215</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>-333</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>-190</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>-365</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>14-JUN-26</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>-383</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>-370</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>-352</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J199" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J201" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>22-JUN-26</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>22-JUN-26</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>22-JUN-26</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>24-JUN-26</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K313" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K315" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K318" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K320" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K321" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K322" s="2" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K327" s="2" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K338" s="2" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K341" s="2" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K342" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K343" s="2" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K344" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K345" s="2" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K346" s="2" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K347" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K349" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K350" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K354" s="2" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K357" s="2" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K362" s="2" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K363" s="2" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K364" s="2" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K365" s="2" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K366" s="2" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K367" s="2" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K368" s="2" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K369" s="2" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K371" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K372" s="2" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K373" s="2" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K374" s="2" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K375" s="2" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K376" s="2" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K378" s="2" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K379" s="2" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K380" s="2" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K381" s="2" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K382" s="2" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K383" s="2" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K384" s="2" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K385" s="2" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K386" s="2" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K387" s="2" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K389" s="2" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K391" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K394" s="2" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K395" s="2" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K396" s="2" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K397" s="2" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K398" s="2" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K399" s="2" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K400" s="2" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K401" s="2" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K402" s="2" t="inlineStr">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K403" s="2" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K405" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K406" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K407" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K408" s="2" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K409" s="2" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K410" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K411" s="2" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K412" s="2" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K413" s="2" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K414" s="2" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K415" s="2" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K416" s="2" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K417" s="2" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K418" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K419" s="2" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K420" s="2" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K421" s="2" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K422" s="2" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K423" s="2" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K424" s="2" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K425" s="2" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K426" s="2" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K427" s="2" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K428" s="2" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K429" s="2" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K430" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K431" s="2" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K432" s="2" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K434" s="2" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K435" s="2" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K436" s="2" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K437" s="2" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K438" s="2" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K439" s="2" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K440" s="2" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K441" s="2" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K442" s="2" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K443" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K444" s="2" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K445" s="2" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K446" s="2" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K447" s="2" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K448" s="2" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K449" s="2" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K450" s="2" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K451" s="2" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K452" s="2" t="inlineStr">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K453" s="2" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="J454" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K454" s="2" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="J455" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K455" s="2" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="J456" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K456" s="2" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="J457" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K457" s="2" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="J458" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K458" s="2" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K459" s="2" t="inlineStr">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="J460" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K460" s="2" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="J461" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K461" s="2" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K463" s="2" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K464" s="2" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K465" s="2" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K466" s="2" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K467" s="2" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="J468" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K468" s="2" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K469" s="2" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K470" s="2" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K471" s="2" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K472" s="2" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K473" s="2" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K474" s="2" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K475" s="2" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K476" s="2" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="J479" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K479" s="2" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="J480" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K480" s="2" t="inlineStr">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="J481" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K481" s="2" t="inlineStr">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K482" s="2" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K483" s="2" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K488" s="2" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K489" s="2" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K490" s="2" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="J491" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K491" s="2" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="J492" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K492" s="2" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="J493" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K493" s="2" t="inlineStr">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="J494" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K494" s="2" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="J495" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K495" s="2" t="inlineStr">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="J496" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K496" s="2" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="J497" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K497" s="2" t="inlineStr">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="J498" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K498" s="2" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="J499" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K499" s="2" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="J500" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K500" s="2" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K501" s="2" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K502" s="2" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K503" s="2" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K504" s="2" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K505" s="2" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="J506" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K506" s="2" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K507" s="2" t="inlineStr">
@@ -23344,7 +23344,7 @@
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K508" s="2" t="inlineStr">

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>flynas XY-583</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>909</v>
+        <v>1253</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-628</v>
+        <v>-284</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1363</v>
+        <v>1253</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-174</v>
+        <v>-284</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>flynas XY-577</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1363</v>
+        <v>1253</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-174</v>
+        <v>-284</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         <v>1248</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1537</v>
+        <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-289</v>
+        <v>-110</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>1248</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1537</v>
+        <v>1358</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-289</v>
+        <v>-110</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -783,10 +783,10 @@
         <v>1248</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1537</v>
+        <v>1358</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-289</v>
+        <v>-110</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>733</v>
+        <v>843</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>708</v>
+        <v>2614</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25</v>
+        <v>-1771</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>flynas XY-573</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>843</v>
+        <v>1003</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1771</v>
+        <v>-1611</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>849</v>
+        <v>1003</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1765</v>
+        <v>-1611</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -960,22 +960,22 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>887</v>
+        <v>1103</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1727</v>
+        <v>-1511</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>933</v>
+        <v>1174</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1681</v>
+        <v>-1440</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>935</v>
+        <v>2641</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1679</v>
+        <v>27</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,33 +1091,393 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2494</v>
+        <v>690</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-120</v>
+        <v>-438</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-438</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-437</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-335</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-328</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-432</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-432</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>495</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-423</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-583</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1253</v>
+        <v>1174</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-284</v>
+        <v>-363</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1253</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-284</v>
+        <v>-174</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -641,28 +641,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-577</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1253</v>
+        <v>1363</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-284</v>
+        <v>-174</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -686,7 +686,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -731,7 +731,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>843</v>
+        <v>647</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1771</v>
+        <v>-1967</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-573</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1003</v>
+        <v>737</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1611</v>
+        <v>-1877</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1003</v>
+        <v>737</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1611</v>
+        <v>-1877</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1103</v>
+        <v>843</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1511</v>
+        <v>-1771</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1174</v>
+        <v>933</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1440</v>
+        <v>-1681</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -1050,26 +1050,26 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2641</v>
+        <v>2494</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>27</v>
+        <v>-120</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>690</v>
+        <v>512</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-438</v>
+        <v>-616</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1157,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-437</v>
+        <v>-438</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,7 +1202,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>793</v>
+        <v>691</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-335</v>
+        <v>-437</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1337,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1472,12 +1472,4692 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-659</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-659</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-177</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-383</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1536</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-328</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-493</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>959</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1169</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-259</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-331</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-177</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-89</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-89</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-89</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-164</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-164</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-164</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-249</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-249</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-249</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-134</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-249</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-205</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-204</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-204</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-69</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-69</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-204</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02-AUG-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>02-AUG-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>02-AUG-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1174</v>
+        <v>1096</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-363</v>
+        <v>-441</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1363</v>
+        <v>1420</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-174</v>
+        <v>-117</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1363</v>
+        <v>1449</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-174</v>
+        <v>-88</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1248</v>
+        <v>1290</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1358</v>
+        <v>1537</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-110</v>
+        <v>-247</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1248</v>
+        <v>1363</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1358</v>
+        <v>1537</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-110</v>
+        <v>-174</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1248</v>
+        <v>1363</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1358</v>
+        <v>1537</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-110</v>
+        <v>-174</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>647</v>
+        <v>733</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2614</v>
+        <v>708</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1967</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>737</v>
+        <v>647</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1877</v>
+        <v>-1967</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>737</v>
+        <v>933</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1877</v>
+        <v>-1681</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>30</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>843</v>
+        <v>935</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1771</v>
+        <v>-1679</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>933</v>
+        <v>1029</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1681</v>
+        <v>-1585</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2494</v>
+        <v>1029</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-120</v>
+        <v>-1585</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>512</v>
+        <v>2641</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128</v>
+        <v>2614</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-616</v>
+        <v>27</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>944</v>
+        <v>579</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>236</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1428</v>
+        <v>708</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-659</v>
+        <v>28</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>769</v>
+        <v>944</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1428</v>
+        <v>708</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-659</v>
+        <v>236</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>933</v>
+        <v>769</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-495</v>
+        <v>-659</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>933</v>
+        <v>769</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-495</v>
+        <v>-659</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-493</v>
+        <v>-495</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-383</v>
+        <v>-495</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1536</v>
+        <v>935</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>108</v>
+        <v>-493</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>933</v>
+        <v>1045</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-495</v>
+        <v>-383</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1877,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-493</v>
+        <v>-495</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-469</v>
+        <v>-493</v>
       </c>
       <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1043</v>
+        <v>1209</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-223</v>
+        <v>-57</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1289</v>
+        <v>1043</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>23</v>
+        <v>-223</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1304</v>
+        <v>1289</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2507,9 +2507,9 @@
       <c r="I45" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>829</v>
+        <v>1304</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>918</v>
+        <v>1266</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-89</v>
+        <v>38</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,9 +2552,9 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>704</v>
+        <v>829</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-64</v>
+        <v>-89</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>834</v>
+        <v>704</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>66</v>
+        <v>-64</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>554</v>
+        <v>944</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-214</v>
+        <v>176</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2867,9 +2867,9 @@
       <c r="I53" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>734</v>
+        <v>604</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-34</v>
+        <v>-164</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-214</v>
+        <v>-34</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-164</v>
+        <v>-214</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-249</v>
+        <v>-164</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>634</v>
+        <v>519</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-134</v>
+        <v>-249</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>519</v>
+        <v>634</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-249</v>
+        <v>-134</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>46</v>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>554</v>
+        <v>736</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-214</v>
+        <v>-32</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>554</v>
+        <v>736</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-214</v>
+        <v>-32</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-205</v>
+        <v>-249</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>46</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-204</v>
+        <v>-214</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-204</v>
+        <v>-214</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,30 +3611,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-189</v>
+        <v>-204</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-303</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>519</v>
+        <v>706</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-189</v>
+        <v>-2</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3677,9 +3677,9 @@
       <c r="I71" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-189</v>
+        <v>-204</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-104</v>
+        <v>-189</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3857,9 +3857,9 @@
       <c r="I75" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,27 +3871,27 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>46</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,27 +3916,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>46</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,27 +3961,27 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-34</v>
+        <v>-104</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>46</v>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,26 +4016,26 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>504</v>
+        <v>770</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-204</v>
+        <v>62</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -4051,12 +4051,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4068,10 +4068,10 @@
         <v>519</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4127,9 +4127,9 @@
       <c r="I81" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,27 +4141,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>498</v>
+        <v>588</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>21</v>
+        <v>-69</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>46</v>
@@ -4186,27 +4186,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>519</v>
+        <v>770</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>498</v>
+        <v>588</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>46</v>
@@ -4231,36 +4231,36 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>21</v>
+        <v>-204</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,30 +4286,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-144</v>
+        <v>-189</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-129</v>
+        <v>-189</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4352,9 +4352,9 @@
       <c r="I86" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Saudia SV-303</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>519</v>
+        <v>706</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-129</v>
+        <v>-2</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>46</v>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-144</v>
+        <v>-129</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-144</v>
+        <v>-129</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-94</v>
+        <v>5</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>46</v>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-94</v>
+        <v>5</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>46</v>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-44</v>
+        <v>21</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>46</v>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,26 +4646,26 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-144</v>
+        <v>21</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -4681,27 +4681,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-129</v>
+        <v>21</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>46</v>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,26 +4736,26 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-129</v>
+        <v>-144</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>736</v>
+        <v>519</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>88</v>
+        <v>-129</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>46</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-44</v>
+        <v>-69</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>46</v>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,26 +4961,26 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>504</v>
+        <v>593</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-144</v>
+        <v>-55</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,26 +5006,26 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-129</v>
+        <v>-144</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-129</v>
+        <v>-94</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>46</v>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>504</v>
+        <v>604</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-144</v>
+        <v>-44</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,26 +5186,26 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-121</v>
+        <v>-144</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-94</v>
+        <v>-69</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,26 +5321,26 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-144</v>
+        <v>-69</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>46</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,26 +5411,26 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-144</v>
+        <v>-94</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,26 +5456,26 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5536,27 +5536,27 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-14</v>
+        <v>-145</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>46</v>
@@ -5581,36 +5581,36 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-14</v>
+        <v>-144</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,30 +5636,30 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>704</v>
+        <v>504</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-214</v>
+        <v>-144</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>704</v>
+        <v>519</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-214</v>
+        <v>-129</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>46</v>
@@ -5702,9 +5702,9 @@
       <c r="I116" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>704</v>
+        <v>503</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-214</v>
+        <v>-145</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>46</v>
@@ -5747,9 +5747,9 @@
       <c r="I117" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>834</v>
+        <v>503</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-84</v>
+        <v>-145</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>46</v>
@@ -5792,9 +5792,9 @@
       <c r="I118" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,26 +5816,26 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-469</v>
+        <v>-129</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>704</v>
+        <v>503</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-214</v>
+        <v>-145</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>46</v>
@@ -5882,9 +5882,9 @@
       <c r="I120" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,30 +5906,30 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>704</v>
+        <v>504</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-214</v>
+        <v>-144</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>704</v>
+        <v>527</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-214</v>
+        <v>-121</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>46</v>
@@ -5972,9 +5972,9 @@
       <c r="I122" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,30 +5996,30 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-414</v>
+        <v>-94</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,26 +6041,26 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-414</v>
+        <v>-145</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-414</v>
+        <v>-145</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -6121,43 +6121,1573 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>09-AUG-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>09-AUG-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>21-AUG-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-668</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D160" s="2" t="n">
         <v>519</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>918</v>
       </c>
-      <c r="F126" s="2" t="n">
+      <c r="F160" s="2" t="n">
         <v>-399</v>
       </c>
-      <c r="G126" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="G160" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>1096</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1537</v>
+        <v>1748</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-441</v>
+        <v>-652</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>20</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flyadeal F3-761</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1420</v>
+        <v>1256</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1537</v>
+        <v>1748</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-117</v>
+        <v>-492</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1449</v>
+        <v>1420</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1537</v>
+        <v>1748</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-88</v>
+        <v>-328</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1290</v>
+        <v>1363</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1537</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-247</v>
+        <v>-174</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -731,7 +731,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>647</v>
+        <v>933</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1967</v>
+        <v>-1681</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1681</v>
+        <v>-1678</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>flynas XY-573</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>935</v>
+        <v>1003</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1679</v>
+        <v>-1611</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>690</v>
+        <v>475</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-438</v>
+        <v>-653</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1202,7 +1202,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-437</v>
+        <v>-438</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>486</v>
+        <v>691</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>918</v>
+        <v>1128</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-432</v>
+        <v>-437</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1337,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-423</v>
+        <v>-432</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>498</v>
+        <v>918</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>21</v>
+        <v>-423</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1472,7 +1472,7 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>588</v>
+        <v>498</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-9</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>736</v>
+        <v>579</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>28</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>944</v>
+        <v>579</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>236</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,7 +1607,7 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1428</v>
+        <v>588</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-659</v>
+        <v>182</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>769</v>
+        <v>706</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1428</v>
+        <v>708</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-659</v>
+        <v>-2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1428</v>
+        <v>708</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-495</v>
+        <v>236</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>933</v>
+        <v>769</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-495</v>
+        <v>-659</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>935</v>
+        <v>769</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-493</v>
+        <v>-659</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-383</v>
+        <v>-495</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1922,7 +1922,7 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-495</v>
+        <v>-493</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1967,7 +1967,7 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>935</v>
+        <v>1045</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-493</v>
+        <v>-383</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1169</v>
+        <v>933</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-259</v>
+        <v>-495</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1043</v>
+        <v>933</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1266</v>
+        <v>1428</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-223</v>
+        <v>-495</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1045</v>
+        <v>935</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1266</v>
+        <v>1428</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-221</v>
+        <v>-493</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1045</v>
+        <v>959</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1266</v>
+        <v>1428</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-221</v>
+        <v>-469</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>935</v>
+        <v>1169</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1266</v>
+        <v>1428</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-331</v>
+        <v>-259</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2327,7 +2327,7 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,28 +2351,28 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1209</v>
+        <v>1045</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-57</v>
+        <v>-221</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1043</v>
+        <v>935</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-223</v>
+        <v>-331</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2417,7 +2417,7 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,28 +2441,28 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1289</v>
+        <v>1043</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>23</v>
+        <v>-223</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,28 +2486,28 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1289</v>
+        <v>1045</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>23</v>
+        <v>-221</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1304</v>
+        <v>1209</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>38</v>
+        <v>-57</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>829</v>
+        <v>1043</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>918</v>
+        <v>1266</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-89</v>
+        <v>-223</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>829</v>
+        <v>1289</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>918</v>
+        <v>1266</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-89</v>
+        <v>23</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>829</v>
+        <v>1289</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>918</v>
+        <v>1266</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-89</v>
+        <v>23</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2687,7 +2687,7 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>704</v>
+        <v>1304</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>768</v>
+        <v>1266</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-64</v>
+        <v>38</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>704</v>
+        <v>829</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-64</v>
+        <v>-89</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2777,7 +2777,7 @@
       <c r="I51" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>704</v>
+        <v>829</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-64</v>
+        <v>-89</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2822,7 +2822,7 @@
       <c r="I52" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>944</v>
+        <v>829</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>176</v>
+        <v>-89</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2867,7 +2867,7 @@
       <c r="I53" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-164</v>
+        <v>-64</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-164</v>
+        <v>-64</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-164</v>
+        <v>-64</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>734</v>
+        <v>944</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-34</v>
+        <v>176</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-214</v>
+        <v>-164</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,7 +3092,7 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-214</v>
+        <v>-164</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3137,7 +3137,7 @@
       <c r="I59" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>519</v>
+        <v>734</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-249</v>
+        <v>-34</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3227,7 +3227,7 @@
       <c r="I61" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-249</v>
+        <v>-214</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,7 +3272,7 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3300,13 +3300,13 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-249</v>
+        <v>-214</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3317,7 +3317,7 @@
       <c r="I63" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-134</v>
+        <v>-164</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>46</v>
@@ -3362,7 +3362,7 @@
       <c r="I64" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>736</v>
+        <v>519</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-32</v>
+        <v>-249</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3407,7 +3407,7 @@
       <c r="I65" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>736</v>
+        <v>519</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-32</v>
+        <v>-249</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       <c r="I66" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -3497,7 +3497,7 @@
       <c r="I67" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>554</v>
+        <v>634</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-214</v>
+        <v>-134</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>46</v>
@@ -3542,7 +3542,7 @@
       <c r="I68" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-214</v>
+        <v>-265</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>46</v>
@@ -3587,7 +3587,7 @@
       <c r="I69" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,30 +3611,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-204</v>
+        <v>-265</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-303</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>706</v>
+        <v>503</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-2</v>
+        <v>-265</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>504</v>
+        <v>736</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-204</v>
+        <v>-32</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-189</v>
+        <v>-205</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>46</v>
@@ -3767,7 +3767,7 @@
       <c r="I73" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-189</v>
+        <v>-205</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>46</v>
@@ -3812,7 +3812,7 @@
       <c r="I74" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-189</v>
+        <v>-205</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3857,7 +3857,7 @@
       <c r="I75" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-189</v>
+        <v>-204</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-189</v>
+        <v>-204</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-104</v>
+        <v>-189</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>46</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>770</v>
+        <v>519</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>62</v>
+        <v>-189</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>46</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,27 +4051,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,27 +4141,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>46</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,27 +4186,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>770</v>
+        <v>604</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>182</v>
+        <v>-104</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>46</v>
@@ -4217,7 +4217,7 @@
       <c r="I83" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4231,38 +4231,38 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-204</v>
+        <v>-69</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4276,27 +4276,27 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>46</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,27 +4321,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,27 +4366,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-303</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>706</v>
+        <v>770</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-2</v>
+        <v>182</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>46</v>
@@ -4397,7 +4397,7 @@
       <c r="I87" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-129</v>
+        <v>-205</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>46</v>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,17 +4466,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-129</v>
+        <v>-205</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>46</v>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>5</v>
+        <v>-205</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>46</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,28 +4556,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>5</v>
+        <v>-204</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>21</v>
+        <v>-205</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>46</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>21</v>
+        <v>-129</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>46</v>
@@ -4667,7 +4667,7 @@
       <c r="I93" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4681,27 +4681,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>21</v>
+        <v>-129</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>46</v>
@@ -4712,7 +4712,7 @@
       <c r="I94" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,28 +4736,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-144</v>
+        <v>5</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4788,10 +4788,10 @@
         <v>519</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-129</v>
+        <v>21</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>46</v>
@@ -4802,7 +4802,7 @@
       <c r="I96" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-129</v>
+        <v>21</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>46</v>
@@ -4847,7 +4847,7 @@
       <c r="I97" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4861,38 +4861,38 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-144</v>
+        <v>21</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>579</v>
+        <v>504</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-69</v>
+        <v>-144</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,28 +4961,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-55</v>
+        <v>-129</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,28 +5006,28 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-144</v>
+        <v>-129</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,28 +5051,28 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-94</v>
+        <v>-55</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-94</v>
+        <v>-145</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>46</v>
@@ -5117,7 +5117,7 @@
       <c r="I103" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="J103" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>604</v>
+        <v>503</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-44</v>
+        <v>-145</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>46</v>
@@ -5162,7 +5162,7 @@
       <c r="I104" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,28 +5186,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,28 +5231,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-94</v>
+        <v>-144</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>579</v>
+        <v>736</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-69</v>
+        <v>88</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5297,7 +5297,7 @@
       <c r="I107" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,28 +5321,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>579</v>
+        <v>504</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-69</v>
+        <v>-144</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>519</v>
+        <v>736</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-129</v>
+        <v>88</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>46</v>
@@ -5387,7 +5387,7 @@
       <c r="I109" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
+      <c r="J109" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -5432,7 +5432,7 @@
       <c r="I110" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J110" s="3" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>46</v>
@@ -5477,7 +5477,7 @@
       <c r="I111" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-145</v>
+        <v>-44</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5522,7 +5522,7 @@
       <c r="I112" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,28 +5546,28 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,28 +5591,28 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-144</v>
+        <v>-94</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,28 +5636,28 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>flynas XY-589</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>504</v>
+        <v>593</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-144</v>
+        <v>-55</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,28 +5681,28 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>503</v>
+        <v>770</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-145</v>
+        <v>122</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>46</v>
@@ -5747,7 +5747,7 @@
       <c r="I117" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
+      <c r="J117" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       <c r="I118" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
+      <c r="J118" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>46</v>
@@ -5837,7 +5837,7 @@
       <c r="I119" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="J119" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>46</v>
@@ -5882,7 +5882,7 @@
       <c r="I120" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,28 +5906,28 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-121</v>
+        <v>-145</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>46</v>
@@ -5972,7 +5972,7 @@
       <c r="I122" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
+      <c r="J122" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,28 +5996,28 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-94</v>
+        <v>-144</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>46</v>
@@ -6062,7 +6062,7 @@
       <c r="I124" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="J124" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,28 +6086,28 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>46</v>
@@ -6152,7 +6152,7 @@
       <c r="I126" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
+      <c r="J126" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>736</v>
+        <v>519</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>88</v>
+        <v>-129</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>46</v>
@@ -6197,7 +6197,7 @@
       <c r="I127" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
+      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>46</v>
@@ -6242,7 +6242,7 @@
       <c r="I128" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6256,27 +6256,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-145</v>
+        <v>-30</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>46</v>
@@ -6287,7 +6287,7 @@
       <c r="I129" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
+      <c r="J129" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6301,27 +6301,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-145</v>
+        <v>-30</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>46</v>
@@ -6332,7 +6332,7 @@
       <c r="I130" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
+      <c r="J130" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6346,38 +6346,38 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-144</v>
+        <v>-30</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       <c r="I132" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
+      <c r="J132" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-145</v>
+        <v>-121</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>46</v>
@@ -6467,7 +6467,7 @@
       <c r="I133" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
+      <c r="J133" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-44</v>
+        <v>-94</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>46</v>
@@ -6512,7 +6512,7 @@
       <c r="I134" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
+      <c r="J134" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>770</v>
+        <v>554</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>122</v>
+        <v>-94</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>46</v>
@@ -6557,7 +6557,7 @@
       <c r="I135" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="J135" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>770</v>
+        <v>503</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>122</v>
+        <v>-145</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>46</v>
@@ -6602,7 +6602,7 @@
       <c r="I136" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
+      <c r="J136" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6616,27 +6616,27 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-30</v>
+        <v>-145</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>46</v>
@@ -6647,7 +6647,7 @@
       <c r="I137" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J137" s="3" t="inlineStr">
+      <c r="J137" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6661,38 +6661,38 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-301</t>
+          <t>flynas XY-577</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>503</v>
+        <v>593</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6706,38 +6706,38 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>736</v>
+        <v>504</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>203</v>
+        <v>-144</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,17 +6761,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>46</v>
@@ -6782,7 +6782,7 @@
       <c r="I140" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
+      <c r="J140" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,28 +6806,28 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>503</v>
+        <v>593</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-145</v>
+        <v>-55</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,28 +6851,28 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,28 +6896,28 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-129</v>
+        <v>-144</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6931,27 +6931,27 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-14</v>
+        <v>-145</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>46</v>
@@ -6962,7 +6962,7 @@
       <c r="I144" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J144" s="3" t="inlineStr">
+      <c r="J144" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6976,27 +6976,27 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-14</v>
+        <v>-145</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>46</v>
@@ -7007,7 +7007,7 @@
       <c r="I145" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J145" s="3" t="inlineStr">
+      <c r="J145" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -7021,27 +7021,27 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>736</v>
+        <v>604</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>203</v>
+        <v>-44</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>46</v>
@@ -7052,7 +7052,7 @@
       <c r="I146" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J146" s="3" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -7066,7 +7066,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
@@ -7097,7 +7097,7 @@
       <c r="I147" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J147" s="3" t="inlineStr">
+      <c r="J147" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -7111,38 +7111,38 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>28-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-30</v>
+        <v>-144</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>704</v>
+        <v>519</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-214</v>
+        <v>-129</v>
       </c>
       <c r="G149" s="2" t="n">
         <v>46</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7211,30 +7211,30 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>704</v>
+        <v>593</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>-214</v>
+        <v>-55</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7256,30 +7256,30 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>704</v>
+        <v>593</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>-214</v>
+        <v>-55</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H151" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7291,27 +7291,27 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>834</v>
+        <v>503</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>-84</v>
+        <v>-30</v>
       </c>
       <c r="G152" s="2" t="n">
         <v>46</v>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7336,38 +7336,38 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>-469</v>
+        <v>-30</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -7381,27 +7381,27 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>704</v>
+        <v>503</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>-214</v>
+        <v>-30</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>46</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7426,27 +7426,27 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>-214</v>
+        <v>203</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>46</v>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7471,27 +7471,27 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>704</v>
+        <v>503</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>-214</v>
+        <v>-30</v>
       </c>
       <c r="G156" s="2" t="n">
         <v>46</v>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7516,40 +7516,40 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>28-AUG-26</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>-414</v>
+        <v>-30</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H157" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7575,26 +7575,26 @@
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>504</v>
+        <v>704</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>-414</v>
+        <v>-214</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H158" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7620,26 +7620,26 @@
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>504</v>
+        <v>704</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>-414</v>
+        <v>-214</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H159" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7651,7 +7651,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7661,33 +7661,663 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>519</v>
+        <v>704</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F160" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-773</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>-219</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>-148</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>-148</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F171" s="2" t="n">
         <v>-399</v>
       </c>
-      <c r="G160" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J160" s="5" t="inlineStr">
+      <c r="G171" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-331</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>-182</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>-182</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1096</v>
+        <v>1363</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1748</v>
+        <v>1537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-652</v>
+        <v>-174</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-761</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1256</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1748</v>
+        <v>1537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-492</v>
+        <v>-174</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1420</v>
+        <v>1363</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1748</v>
+        <v>1537</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-328</v>
+        <v>-174</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1363</v>
+        <v>733</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1537</v>
+        <v>708</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-174</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1363</v>
+        <v>849</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1537</v>
+        <v>734</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-174</v>
+        <v>115</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1363</v>
+        <v>684</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1537</v>
+        <v>2614</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-174</v>
+        <v>-1930</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>708</v>
+        <v>2614</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25</v>
+        <v>-1877</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>933</v>
+        <v>737</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1681</v>
+        <v>-1877</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1678</v>
+        <v>-1681</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-573</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1003</v>
+        <v>935</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1611</v>
+        <v>-1679</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1029</v>
+        <v>2494</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1585</v>
+        <v>-120</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1029</v>
+        <v>475</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1585</v>
+        <v>-653</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2641</v>
+        <v>690</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>27</v>
+        <v>-438</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>475</v>
+        <v>690</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-653</v>
+        <v>-438</v>
       </c>
       <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>30</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-438</v>
+        <v>-437</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>690</v>
+        <v>486</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1128</v>
+        <v>918</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-438</v>
+        <v>-432</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>691</v>
+        <v>495</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1128</v>
+        <v>918</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-437</v>
+        <v>-423</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>486</v>
+        <v>601</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-432</v>
+        <v>-317</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>918</v>
+        <v>498</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-432</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>918</v>
+        <v>498</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-423</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>519</v>
+        <v>706</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>21</v>
+        <v>-2</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>519</v>
+        <v>944</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>498</v>
+        <v>708</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>579</v>
+        <v>769</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>588</v>
+        <v>1428</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9</v>
+        <v>-659</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>579</v>
+        <v>769</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>588</v>
+        <v>1428</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-9</v>
+        <v>-659</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>770</v>
+        <v>933</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>588</v>
+        <v>1428</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>182</v>
+        <v>-495</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>706</v>
+        <v>1339</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-2</v>
+        <v>-89</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>944</v>
+        <v>1536</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>769</v>
+        <v>1536</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-659</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>769</v>
+        <v>933</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-659</v>
+        <v>-495</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-495</v>
+        <v>-493</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>933</v>
+        <v>1045</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-495</v>
+        <v>-383</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-493</v>
+        <v>-495</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-383</v>
+        <v>-495</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-495</v>
+        <v>-493</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>933</v>
+        <v>959</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-495</v>
+        <v>-469</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>935</v>
+        <v>1169</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-493</v>
+        <v>-259</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>959</v>
+        <v>1043</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-469</v>
+        <v>-223</v>
       </c>
       <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>30</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1169</v>
+        <v>1045</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-259</v>
+        <v>-221</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-223</v>
+        <v>-221</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>30</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1045</v>
+        <v>935</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-221</v>
+        <v>-331</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-221</v>
+        <v>-223</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>30</v>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>935</v>
+        <v>1045</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-331</v>
+        <v>-221</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1045</v>
+        <v>1289</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-221</v>
+        <v>23</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1209</v>
+        <v>1289</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-57</v>
+        <v>23</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1043</v>
+        <v>1304</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-223</v>
+        <v>38</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1289</v>
+        <v>829</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1266</v>
+        <v>918</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>23</v>
+        <v>-89</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1289</v>
+        <v>829</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1266</v>
+        <v>918</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>23</v>
+        <v>-89</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1304</v>
+        <v>829</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1266</v>
+        <v>918</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>38</v>
+        <v>-89</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2732,9 +2732,9 @@
       <c r="I50" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>829</v>
+        <v>704</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-89</v>
+        <v>-64</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>829</v>
+        <v>704</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-89</v>
+        <v>-64</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>829</v>
+        <v>704</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-89</v>
+        <v>-64</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>704</v>
+        <v>944</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-64</v>
+        <v>176</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>704</v>
+        <v>604</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-64</v>
+        <v>-164</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>704</v>
+        <v>604</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-64</v>
+        <v>-164</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>944</v>
+        <v>604</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>176</v>
+        <v>-164</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3047,9 +3047,9 @@
       <c r="I57" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>604</v>
+        <v>734</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-164</v>
+        <v>-34</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>604</v>
+        <v>736</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-164</v>
+        <v>-32</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-164</v>
+        <v>-214</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>734</v>
+        <v>554</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-34</v>
+        <v>-214</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-214</v>
+        <v>-164</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-214</v>
+        <v>-249</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-164</v>
+        <v>-249</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>46</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>519</v>
+        <v>634</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-249</v>
+        <v>-134</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>634</v>
+        <v>554</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-134</v>
+        <v>-214</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>46</v>
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-265</v>
+        <v>-214</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>46</v>
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>503</v>
+        <v>736</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-265</v>
+        <v>-32</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>46</v>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-265</v>
+        <v>-205</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>736</v>
+        <v>504</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-32</v>
+        <v>-204</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-205</v>
+        <v>-204</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-205</v>
+        <v>-189</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>46</v>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-205</v>
+        <v>-189</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-204</v>
+        <v>-189</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-204</v>
+        <v>-189</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-189</v>
+        <v>-104</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>46</v>
@@ -4037,9 +4037,9 @@
       <c r="I79" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,27 +4051,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4127,9 +4127,9 @@
       <c r="I81" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,27 +4141,27 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-189</v>
+        <v>-69</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>46</v>
@@ -4172,9 +4172,9 @@
       <c r="I82" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,26 +4196,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>604</v>
+        <v>504</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-104</v>
+        <v>-204</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4231,12 +4231,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4248,10 +4248,10 @@
         <v>519</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4262,9 +4262,9 @@
       <c r="I84" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,27 +4276,27 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-69</v>
+        <v>-189</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>46</v>
@@ -4307,9 +4307,9 @@
       <c r="I85" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,27 +4321,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>519</v>
+        <v>736</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>588</v>
+        <v>498</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-69</v>
+        <v>238</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4366,27 +4366,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>770</v>
+        <v>519</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>588</v>
+        <v>498</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>46</v>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>708</v>
+        <v>498</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-205</v>
+        <v>21</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>46</v>
@@ -4442,9 +4442,9 @@
       <c r="I88" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,27 +4456,27 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>708</v>
+        <v>498</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-205</v>
+        <v>21</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>46</v>
@@ -4487,9 +4487,9 @@
       <c r="I89" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-205</v>
+        <v>-145</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>46</v>
@@ -4532,9 +4532,9 @@
       <c r="I90" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4563,10 +4563,10 @@
         <v>504</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-204</v>
+        <v>-144</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>23</v>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-205</v>
+        <v>-129</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>46</v>
@@ -4622,9 +4622,9 @@
       <c r="I92" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,14 +4646,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>-129</v>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>46</v>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4743,10 +4743,10 @@
         <v>503</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>5</v>
+        <v>-145</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>46</v>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>21</v>
+        <v>-145</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>46</v>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,26 +4826,26 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>21</v>
+        <v>-144</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -4861,36 +4861,36 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>21</v>
+        <v>-144</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,26 +4916,26 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>504</v>
+        <v>593</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-144</v>
+        <v>-55</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,26 +4961,26 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,26 +5006,26 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,26 +5051,26 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-55</v>
+        <v>-94</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>46</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-145</v>
+        <v>-44</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>46</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>736</v>
+        <v>554</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>88</v>
+        <v>-94</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,26 +5321,26 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-144</v>
+        <v>-69</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>736</v>
+        <v>503</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>88</v>
+        <v>-145</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>46</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-94</v>
+        <v>-145</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>46</v>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>46</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>604</v>
+        <v>736</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-44</v>
+        <v>88</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>46</v>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-589</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,26 +5681,26 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-55</v>
+        <v>-44</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,26 +5726,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>770</v>
+        <v>504</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>122</v>
+        <v>-144</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>46</v>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>46</v>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-129</v>
+        <v>-121</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>46</v>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-144</v>
+        <v>-94</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>46</v>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>46</v>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,26 +6221,26 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-94</v>
+        <v>-144</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -6256,27 +6256,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-30</v>
+        <v>-94</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>46</v>
@@ -6301,36 +6301,36 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>503</v>
+        <v>593</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -6346,36 +6346,36 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-30</v>
+        <v>-144</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-121</v>
+        <v>-145</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>46</v>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-94</v>
+        <v>-69</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>46</v>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,26 +6536,26 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-94</v>
+        <v>-144</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>46</v>
@@ -6616,27 +6616,27 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-145</v>
+        <v>-14</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>46</v>
@@ -6661,36 +6661,36 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-577</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-55</v>
+        <v>-14</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -6706,36 +6706,36 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>504</v>
+        <v>736</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-144</v>
+        <v>203</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,17 +6761,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>554</v>
+        <v>704</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-94</v>
+        <v>-214</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>46</v>
@@ -6782,9 +6782,9 @@
       <c r="I140" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>593</v>
+        <v>704</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-55</v>
+        <v>-214</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>503</v>
+        <v>704</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-145</v>
+        <v>-214</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>46</v>
@@ -6872,9 +6872,9 @@
       <c r="I142" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6900,26 +6900,26 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>504</v>
+        <v>834</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-144</v>
+        <v>-84</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>503</v>
+        <v>704</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-145</v>
+        <v>-214</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>46</v>
@@ -6962,9 +6962,9 @@
       <c r="I144" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6986,17 +6986,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>503</v>
+        <v>704</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-145</v>
+        <v>-214</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>46</v>
@@ -7007,9 +7007,9 @@
       <c r="I145" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-44</v>
+        <v>-214</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>46</v>
@@ -7052,9 +7052,9 @@
       <c r="I146" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7066,27 +7066,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>533</v>
+        <v>918</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-30</v>
+        <v>-415</v>
       </c>
       <c r="G147" s="2" t="n">
         <v>46</v>
@@ -7097,9 +7097,9 @@
       <c r="I147" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7128,10 +7128,10 @@
         <v>504</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-144</v>
+        <v>-414</v>
       </c>
       <c r="G148" s="2" t="n">
         <v>23</v>
@@ -7142,9 +7142,9 @@
       <c r="I148" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-129</v>
+        <v>-399</v>
       </c>
       <c r="G149" s="2" t="n">
         <v>46</v>
@@ -7187,9 +7187,9 @@
       <c r="I149" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7218,10 +7218,10 @@
         <v>593</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>-55</v>
+        <v>-325</v>
       </c>
       <c r="G150" s="2" t="n">
         <v>40</v>
@@ -7232,9 +7232,9 @@
       <c r="I150" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7256,1068 +7256,33 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>593</v>
+        <v>736</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>-55</v>
+        <v>-182</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H151" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-309</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-389</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-301</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-411</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>736</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>28-AUG-26</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-383</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>28-AUG-26</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-387</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E159" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E160" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="E161" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>-84</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-773</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="n">
-        <v>699</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>-219</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E164" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-331</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="E166" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>-148</v>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H166" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I166" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-411</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>-148</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H167" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I167" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-309</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F168" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H168" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I168" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J168" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-305</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H169" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I169" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J169" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E170" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F170" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H170" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I170" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-668</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>-399</v>
-      </c>
-      <c r="G171" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H171" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J171" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-331</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="n">
-        <v>736</v>
-      </c>
-      <c r="E172" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>-182</v>
-      </c>
-      <c r="G172" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H172" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I172" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J172" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-411</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="n">
-        <v>736</v>
-      </c>
-      <c r="E173" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F173" s="2" t="n">
-        <v>-182</v>
-      </c>
-      <c r="G173" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H173" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I173" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J173" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-326</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="n">
-        <v>868</v>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F174" s="2" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G174" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H174" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I174" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J174" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K174" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -48,12 +48,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -62,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1363</v>
+        <v>379</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1537</v>
+        <v>734</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-174</v>
+        <v>-355</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1363</v>
+        <v>486</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1537</v>
+        <v>734</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-174</v>
+        <v>-248</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1363</v>
+        <v>589</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1537</v>
+        <v>2614</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-174</v>
+        <v>-2025</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>733</v>
+        <v>589</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>708</v>
+        <v>2614</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>25</v>
+        <v>-2025</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>849</v>
+        <v>601</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>734</v>
+        <v>2614</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>115</v>
+        <v>-2013</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>684</v>
+        <v>645</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1930</v>
+        <v>-1969</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -821,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>737</v>
+        <v>670</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1877</v>
+        <v>-1944</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>737</v>
+        <v>2239</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2614</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1877</v>
+        <v>-375</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>933</v>
+        <v>400</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1681</v>
+        <v>-728</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>935</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1679</v>
+        <v>-728</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2494</v>
+        <v>475</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2614</v>
+        <v>1128</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-120</v>
+        <v>-653</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1128</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-653</v>
+        <v>-642</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>690</v>
+        <v>400</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128</v>
+        <v>918</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-438</v>
+        <v>-518</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,7 +1112,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>690</v>
+        <v>486</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1128</v>
+        <v>918</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-438</v>
+        <v>-432</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>691</v>
+        <v>486</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1128</v>
+        <v>918</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-437</v>
+        <v>-432</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,7 +1202,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>486</v>
+        <v>591</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>918</v>
+        <v>708</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-432</v>
+        <v>-117</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>495</v>
+        <v>591</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>918</v>
+        <v>708</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-423</v>
+        <v>-117</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>918</v>
+        <v>708</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-317</v>
+        <v>-117</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>519</v>
+        <v>691</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>498</v>
+        <v>1014</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>21</v>
+        <v>-323</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>519</v>
+        <v>691</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>498</v>
+        <v>1014</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>21</v>
+        <v>-323</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>708</v>
+        <v>1014</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2</v>
+        <v>-323</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>944</v>
+        <v>791</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>236</v>
+        <v>-637</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-659</v>
+        <v>-637</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-659</v>
+        <v>-637</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>933</v>
+        <v>962</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-495</v>
+        <v>-466</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1339</v>
+        <v>691</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-89</v>
+        <v>-737</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1536</v>
+        <v>791</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>108</v>
+        <v>-637</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1536</v>
+        <v>791</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>108</v>
+        <v>-637</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>933</v>
+        <v>962</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-495</v>
+        <v>-466</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-493</v>
+        <v>-466</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1045</v>
+        <v>791</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-383</v>
+        <v>-637</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>933</v>
+        <v>791</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-495</v>
+        <v>-637</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>933</v>
+        <v>791</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-495</v>
+        <v>-637</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>935</v>
+        <v>959</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-493</v>
+        <v>-469</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>959</v>
+        <v>1521</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-469</v>
+        <v>93</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1169</v>
+        <v>791</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-259</v>
+        <v>-475</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,7 +2147,7 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1043</v>
+        <v>791</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-223</v>
+        <v>-475</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1045</v>
+        <v>791</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-221</v>
+        <v>-475</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1045</v>
+        <v>791</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-221</v>
+        <v>-475</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>935</v>
+        <v>791</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-331</v>
+        <v>-475</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1043</v>
+        <v>791</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-223</v>
+        <v>-475</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2396,28 +2396,28 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-177</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1045</v>
+        <v>796</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-221</v>
+        <v>-470</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1043</v>
+        <v>691</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-223</v>
+        <v>-575</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1289</v>
+        <v>691</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>23</v>
+        <v>-575</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1289</v>
+        <v>691</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>23</v>
+        <v>-575</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1304</v>
+        <v>741</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>38</v>
+        <v>-27</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>46</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>829</v>
+        <v>741</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-89</v>
+        <v>-27</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>829</v>
+        <v>741</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-89</v>
+        <v>-27</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2687,7 +2687,7 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>829</v>
+        <v>641</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-89</v>
+        <v>-127</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2732,7 +2732,7 @@
       <c r="I50" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>704</v>
+        <v>641</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-64</v>
+        <v>-127</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2777,7 +2777,7 @@
       <c r="I51" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>704</v>
+        <v>641</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-64</v>
+        <v>-127</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2822,7 +2822,7 @@
       <c r="I52" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>704</v>
+        <v>771</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-64</v>
+        <v>3</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2867,9 +2867,9 @@
       <c r="I53" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>944</v>
+        <v>641</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>176</v>
+        <v>-127</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2912,7 +2912,7 @@
       <c r="I54" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-164</v>
+        <v>-127</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-164</v>
+        <v>-127</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-164</v>
+        <v>-212</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3047,7 +3047,7 @@
       <c r="I57" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>734</v>
+        <v>556</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-34</v>
+        <v>-212</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,7 +3092,7 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>736</v>
+        <v>556</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-32</v>
+        <v>-212</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3137,7 +3137,7 @@
       <c r="I59" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>554</v>
+        <v>771</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-214</v>
+        <v>3</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-214</v>
+        <v>-212</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3227,7 +3227,7 @@
       <c r="I61" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-164</v>
+        <v>-177</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,7 +3272,7 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-249</v>
+        <v>-177</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3317,7 +3317,7 @@
       <c r="I63" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-249</v>
+        <v>-167</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-249</v>
+        <v>-152</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3435,26 +3435,26 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>634</v>
+        <v>541</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-134</v>
+        <v>-167</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-249</v>
+        <v>-152</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>46</v>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-214</v>
+        <v>-152</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>46</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-214</v>
+        <v>-152</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>46</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>736</v>
+        <v>556</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-32</v>
+        <v>-152</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>46</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-205</v>
+        <v>-152</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>46</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,28 +3701,28 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>504</v>
+        <v>741</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-204</v>
+        <v>33</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3736,38 +3736,38 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-204</v>
+        <v>-32</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3781,27 +3781,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-189</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>46</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,27 +3826,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-189</v>
+        <v>3</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-189</v>
+        <v>-205</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>46</v>
@@ -3902,7 +3902,7 @@
       <c r="I76" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-189</v>
+        <v>-167</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-189</v>
+        <v>-152</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>46</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-104</v>
+        <v>-152</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>46</v>
@@ -4037,7 +4037,7 @@
       <c r="I79" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4051,27 +4051,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>519</v>
+        <v>736</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-69</v>
+        <v>28</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-69</v>
+        <v>-129</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4127,7 +4127,7 @@
       <c r="I81" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4141,38 +4141,38 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>519</v>
+        <v>648</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-69</v>
+        <v>-60</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-204</v>
+        <v>-107</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>23</v>
@@ -4217,7 +4217,7 @@
       <c r="I83" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-189</v>
+        <v>-92</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-189</v>
+        <v>-92</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>46</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>736</v>
+        <v>503</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>238</v>
+        <v>-145</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4352,7 +4352,7 @@
       <c r="I86" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,28 +4376,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>21</v>
+        <v>-107</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,28 +4421,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>21</v>
+        <v>-107</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4456,27 +4456,27 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>21</v>
+        <v>-69</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>46</v>
@@ -4487,7 +4487,7 @@
       <c r="I89" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>503</v>
+        <v>591</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-145</v>
+        <v>-57</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>46</v>
@@ -4532,7 +4532,7 @@
       <c r="I90" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,28 +4556,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>504</v>
+        <v>591</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-144</v>
+        <v>-57</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,28 +4601,28 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-129</v>
+        <v>-107</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4650,13 +4650,13 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-129</v>
+        <v>-57</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>46</v>
@@ -4667,7 +4667,7 @@
       <c r="I93" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-145</v>
+        <v>-92</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>46</v>
@@ -4712,7 +4712,7 @@
       <c r="I94" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>503</v>
+        <v>591</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-145</v>
+        <v>-57</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>46</v>
@@ -4757,7 +4757,7 @@
       <c r="I95" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,28 +4781,28 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-301</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>503</v>
+        <v>709</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-145</v>
+        <v>61</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4830,13 +4830,13 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-144</v>
+        <v>-107</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>23</v>
@@ -4847,7 +4847,7 @@
       <c r="I97" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4875,13 +4875,13 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-144</v>
+        <v>-107</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>23</v>
@@ -4892,7 +4892,7 @@
       <c r="I98" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-565</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-55</v>
+        <v>-92</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,28 +4961,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-55</v>
+        <v>-69</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,28 +5006,28 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-94</v>
+        <v>-57</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>46</v>
@@ -5072,7 +5072,7 @@
       <c r="I102" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-94</v>
+        <v>-145</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>46</v>
@@ -5117,7 +5117,7 @@
       <c r="I103" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>604</v>
+        <v>503</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-44</v>
+        <v>-145</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>46</v>
@@ -5162,7 +5162,7 @@
       <c r="I104" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,28 +5186,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-145</v>
+        <v>-107</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,28 +5231,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-144</v>
+        <v>-92</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-94</v>
+        <v>-145</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5297,7 +5297,7 @@
       <c r="I107" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
+      <c r="J107" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-69</v>
+        <v>-145</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>46</v>
@@ -5342,7 +5342,7 @@
       <c r="I108" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,28 +5366,28 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-145</v>
+        <v>-107</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-145</v>
+        <v>-92</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>46</v>
@@ -5432,7 +5432,7 @@
       <c r="I110" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,28 +5456,28 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-129</v>
+        <v>-107</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>736</v>
+        <v>641</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>88</v>
+        <v>-7</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5522,7 +5522,7 @@
       <c r="I112" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,28 +5546,28 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>504</v>
+        <v>770</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-144</v>
+        <v>122</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,28 +5591,28 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-129</v>
+        <v>-107</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,28 +5636,28 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-55</v>
+        <v>-92</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5671,27 +5671,27 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>604</v>
+        <v>503</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-44</v>
+        <v>-30</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>46</v>
@@ -5702,7 +5702,7 @@
       <c r="I116" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5716,38 +5716,38 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>648</v>
+        <v>533</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-144</v>
+        <v>23</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,30 +5771,30 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-577</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>519</v>
+        <v>608</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-129</v>
+        <v>-310</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>503</v>
+        <v>741</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-145</v>
+        <v>-177</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>46</v>
@@ -5837,9 +5837,9 @@
       <c r="I119" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>519</v>
+        <v>741</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-129</v>
+        <v>-177</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>46</v>
@@ -5882,9 +5882,9 @@
       <c r="I120" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>554</v>
+        <v>871</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-94</v>
+        <v>-47</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>46</v>
@@ -5927,9 +5927,9 @@
       <c r="I121" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,30 +5951,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>503</v>
+        <v>699</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-145</v>
+        <v>-219</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-2</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,30 +5996,30 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>504</v>
+        <v>741</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-144</v>
+        <v>-177</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>527</v>
+        <v>741</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-121</v>
+        <v>-177</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>46</v>
@@ -6062,9 +6062,9 @@
       <c r="I124" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>554</v>
+        <v>741</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-94</v>
+        <v>-177</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>46</v>
@@ -6107,9 +6107,9 @@
       <c r="I125" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,28 +6131,28 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-145</v>
+        <v>-439</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,30 +6176,30 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-145</v>
+        <v>-377</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,30 +6221,30 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-144</v>
+        <v>-362</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,28 +6266,28 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-94</v>
+        <v>-332</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,978 +6311,33 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>flyadeal F3-773</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>593</v>
+        <v>839</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-55</v>
+        <v>-79</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-309</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-383</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-387</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>579</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>-69</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>-129</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>-14</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-666</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>-14</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>21-AUG-26</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>SM-458</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-411</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>736</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>-84</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-383</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J147" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-656</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-668</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>-399</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-565</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>-325</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-331</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>736</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>-182</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J151" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>734</v>
+        <v>463</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-355</v>
+        <v>-64</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-177</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>486</v>
+        <v>400</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>734</v>
+        <v>463</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-248</v>
+        <v>-63</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>589</v>
+        <v>400</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2614</v>
+        <v>463</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2025</v>
+        <v>-63</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,40 +676,40 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-478</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>589</v>
+        <v>400</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2614</v>
+        <v>463</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2025</v>
+        <v>-63</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,40 +721,40 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-478</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>601</v>
+        <v>493</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2614</v>
+        <v>463</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2013</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>645</v>
+        <v>493</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2614</v>
+        <v>463</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1969</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>670</v>
+        <v>514</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2614</v>
+        <v>498</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1944</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-411</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2239</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2614</v>
+        <v>463</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-375</v>
+        <v>-64</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -918,23 +918,23 @@
         <v>400</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1128</v>
+        <v>463</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-728</v>
+        <v>-63</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-328</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>400</v>
+        <v>486</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1128</v>
+        <v>768</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-728</v>
+        <v>-282</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1128</v>
+        <v>768</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-653</v>
+        <v>-273</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1128</v>
+        <v>768</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-642</v>
+        <v>-273</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>400</v>
+        <v>634</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-518</v>
+        <v>-284</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,28 +1136,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-328</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>486</v>
+        <v>634</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-432</v>
+        <v>-284</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>486</v>
+        <v>634</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-432</v>
+        <v>-284</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-117</v>
+        <v>-794</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>591</v>
+        <v>700</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-117</v>
+        <v>-728</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>591</v>
+        <v>700</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>708</v>
+        <v>1428</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-117</v>
+        <v>-728</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>691</v>
+        <v>910</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1014</v>
+        <v>1428</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-323</v>
+        <v>-518</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>Saudia SV-411</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>691</v>
+        <v>910</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1014</v>
+        <v>1428</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-323</v>
+        <v>-518</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>691</v>
+        <v>962</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1014</v>
+        <v>1428</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-323</v>
+        <v>-466</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-637</v>
+        <v>-794</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-637</v>
+        <v>-794</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,7 +1562,7 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-637</v>
+        <v>-794</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,7 +1607,7 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>962</v>
+        <v>802</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-466</v>
+        <v>-626</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Air Arabia Egypt E5-322</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>691</v>
+        <v>802</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1428</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-737</v>
+        <v>-626</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>791</v>
+        <v>700</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1428</v>
+        <v>1014</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-637</v>
+        <v>-314</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>791</v>
+        <v>700</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1428</v>
+        <v>1014</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-637</v>
+        <v>-314</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>962</v>
+        <v>700</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1428</v>
+        <v>1014</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-466</v>
+        <v>-314</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-322</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>962</v>
+        <v>700</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-466</v>
+        <v>-566</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-637</v>
+        <v>-497</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,7 +1922,7 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-637</v>
+        <v>-497</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,7 +1967,7 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>791</v>
+        <v>700</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-637</v>
+        <v>-566</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,7 +2012,7 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>959</v>
+        <v>700</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-469</v>
+        <v>-566</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1521</v>
+        <v>700</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1428</v>
+        <v>1266</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>93</v>
+        <v>-566</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-475</v>
+        <v>-632</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,7 +2147,7 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-475</v>
+        <v>-632</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2192,7 +2192,7 @@
       <c r="I38" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>791</v>
+        <v>634</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-475</v>
+        <v>-632</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2237,7 +2237,7 @@
       <c r="I39" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>791</v>
+        <v>1484</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1266</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-475</v>
+        <v>218</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>46</v>
@@ -2282,9 +2282,9 @@
       <c r="I40" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>791</v>
+        <v>604</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-475</v>
+        <v>-164</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>791</v>
+        <v>604</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-475</v>
+        <v>-164</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>796</v>
+        <v>679</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-470</v>
+        <v>-89</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>691</v>
+        <v>748</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-575</v>
+        <v>-20</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>691</v>
+        <v>544</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-575</v>
+        <v>-224</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>691</v>
+        <v>544</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1266</v>
+        <v>768</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-575</v>
+        <v>-224</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>741</v>
+        <v>544</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-27</v>
+        <v>-224</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>46</v>
@@ -2597,9 +2597,9 @@
       <c r="I47" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>741</v>
+        <v>682</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-27</v>
+        <v>-86</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,9 +2642,9 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>741</v>
+        <v>544</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-27</v>
+        <v>-224</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2687,9 +2687,9 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>641</v>
+        <v>544</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-127</v>
+        <v>-224</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2732,9 +2732,9 @@
       <c r="I50" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>641</v>
+        <v>604</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-127</v>
+        <v>-164</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2777,9 +2777,9 @@
       <c r="I51" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>641</v>
+        <v>493</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-127</v>
+        <v>-275</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>771</v>
+        <v>514</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>3</v>
+        <v>-254</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2867,7 +2867,7 @@
       <c r="I53" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>641</v>
+        <v>514</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-127</v>
+        <v>-254</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-127</v>
+        <v>-146</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>641</v>
+        <v>493</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-127</v>
+        <v>-275</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-212</v>
+        <v>-275</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3047,7 +3047,7 @@
       <c r="I57" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-212</v>
+        <v>-275</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,7 +3092,7 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>556</v>
+        <v>484</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-212</v>
+        <v>-224</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>771</v>
+        <v>493</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>3</v>
+        <v>-215</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3227,7 +3227,7 @@
       <c r="I61" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-177</v>
+        <v>-215</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,7 +3272,7 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,30 +3296,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>591</v>
+        <v>484</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-177</v>
+        <v>-224</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-167</v>
+        <v>-215</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-152</v>
+        <v>-194</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-167</v>
+        <v>-194</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-331</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>556</v>
+        <v>749</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-152</v>
+        <v>41</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>46</v>
@@ -3511,27 +3511,27 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-152</v>
+        <v>-95</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>46</v>
@@ -3556,12 +3556,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-152</v>
+        <v>-95</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>46</v>
@@ -3601,27 +3601,27 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>708</v>
+        <v>588</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-152</v>
+        <v>-74</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>46</v>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,26 +3656,26 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>556</v>
+        <v>484</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-152</v>
+        <v>-224</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>741</v>
+        <v>493</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>708</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>33</v>
+        <v>-215</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>46</v>
@@ -3722,9 +3722,9 @@
       <c r="I72" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,27 +3736,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-32</v>
+        <v>-194</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>46</v>
@@ -3767,9 +3767,9 @@
       <c r="I73" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,27 +3781,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>588</v>
+        <v>498</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>46</v>
@@ -3826,27 +3826,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>588</v>
+        <v>498</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-301</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>708</v>
+        <v>498</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-205</v>
+        <v>-5</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>46</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,26 +3926,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>708</v>
+        <v>498</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-167</v>
+        <v>16</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>556</v>
+        <v>514</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>708</v>
+        <v>498</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-152</v>
+        <v>16</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>46</v>
@@ -4006,27 +4006,27 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>708</v>
+        <v>533</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-152</v>
+        <v>-40</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>46</v>
@@ -4051,27 +4051,27 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>736</v>
+        <v>493</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>708</v>
+        <v>533</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>28</v>
+        <v>-40</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46</v>
@@ -4082,9 +4082,9 @@
       <c r="I80" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,27 +4096,27 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-389</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>579</v>
+        <v>514</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>708</v>
+        <v>533</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-129</v>
+        <v>-19</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,26 +4151,26 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
+        <v>484</v>
+      </c>
+      <c r="E82" s="2" t="n">
         <v>648</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>708</v>
-      </c>
       <c r="F82" s="2" t="n">
-        <v>-60</v>
+        <v>-164</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -4196,26 +4196,26 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-107</v>
+        <v>-155</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-92</v>
+        <v>-155</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-92</v>
+        <v>-155</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>46</v>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-145</v>
+        <v>-155</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,26 +4376,26 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-107</v>
+        <v>-152</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Air Arabia Egypt E5-326</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>541</v>
+        <v>709</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-107</v>
+        <v>61</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>579</v>
+        <v>484</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-69</v>
+        <v>-164</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>591</v>
+        <v>496</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-57</v>
+        <v>-152</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>46</v>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,26 +4556,26 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>591</v>
+        <v>484</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-57</v>
+        <v>-164</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,26 +4601,26 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-107</v>
+        <v>-134</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-57</v>
+        <v>-134</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>46</v>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-92</v>
+        <v>-104</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>46</v>
@@ -4726,27 +4726,27 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-57</v>
+        <v>-5</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>46</v>
@@ -4771,36 +4771,36 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-326</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>709</v>
+        <v>493</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>61</v>
+        <v>-5</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -4816,36 +4816,36 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-107</v>
+        <v>16</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,26 +4871,26 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-107</v>
+        <v>-152</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,26 +4916,26 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>556</v>
+        <v>504</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-92</v>
+        <v>-144</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-69</v>
+        <v>-129</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>46</v>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>591</v>
+        <v>519</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-57</v>
+        <v>-129</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>46</v>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>591</v>
+        <v>554</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-57</v>
+        <v>-94</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>46</v>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-145</v>
+        <v>-152</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>46</v>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5190,13 +5190,13 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-107</v>
+        <v>-144</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>23</v>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-92</v>
+        <v>-129</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>46</v>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>46</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,26 +5366,26 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-107</v>
+        <v>-94</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,26 +5411,26 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>556</v>
+        <v>504</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-92</v>
+        <v>-144</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,26 +5456,26 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-107</v>
+        <v>-129</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5505,13 +5505,13 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>641</v>
+        <v>527</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-7</v>
+        <v>-121</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-331</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>770</v>
+        <v>554</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>122</v>
+        <v>-94</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>46</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,26 +5591,26 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-107</v>
+        <v>-152</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,26 +5636,26 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>556</v>
+        <v>504</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-92</v>
+        <v>-144</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -5671,27 +5671,27 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-30</v>
+        <v>-129</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>46</v>
@@ -5716,27 +5716,27 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>21-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SM-458</t>
+          <t>SM-452</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>23</v>
+        <v>-94</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>46</v>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,30 +5771,30 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-577</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>608</v>
+        <v>568</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-310</v>
+        <v>-80</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>741</v>
+        <v>604</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-177</v>
+        <v>-44</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>46</v>
@@ -5837,9 +5837,9 @@
       <c r="I119" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,27 +5851,27 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>741</v>
+        <v>496</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-177</v>
+        <v>-37</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>46</v>
@@ -5882,9 +5882,9 @@
       <c r="I120" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,27 +5896,27 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>871</v>
+        <v>554</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-47</v>
+        <v>21</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>46</v>
@@ -5927,9 +5927,9 @@
       <c r="I121" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,30 +5951,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-773</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>699</v>
+        <v>496</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-219</v>
+        <v>-152</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,30 +5996,30 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>741</v>
+        <v>504</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-177</v>
+        <v>-144</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>741</v>
+        <v>519</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-177</v>
+        <v>-129</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>46</v>
@@ -6062,9 +6062,9 @@
       <c r="I124" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>16-AUG-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>741</v>
+        <v>496</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-177</v>
+        <v>33</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>46</v>
@@ -6107,9 +6107,9 @@
       <c r="I125" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>16-AUG-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,26 +6131,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-439</v>
+        <v>33</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -6166,40 +6166,40 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>21-AUG-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SM-452</t>
+          <t>SM-458</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>918</v>
+        <v>533</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-377</v>
+        <v>-14</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-362</v>
+        <v>33</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>46</v>
@@ -6242,9 +6242,9 @@
       <c r="I128" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,26 +6266,26 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>586</v>
+        <v>496</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-332</v>
+        <v>33</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -6301,43 +6301,1258 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23-AUG-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>23-AUG-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>26-AUG-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-37</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-37</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>13-SEP-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>13-SEP-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>13-SEP-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-458</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>21-SEP-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-411</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>SM-452</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-773</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>839</v>
-      </c>
-      <c r="E130" s="2" t="n">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E154" s="2" t="n">
         <v>918</v>
       </c>
-      <c r="F130" s="2" t="n">
-        <v>-79</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="F154" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-452</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>-305</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
